--- a/information_request_forms/008_education_content_distribution_request_form--information_request_forms.xlsx
+++ b/information_request_forms/008_education_content_distribution_request_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'document'}</t>
+          <t>document</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Document'}</t>
+          <t>Document</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'needs_assessment'}</t>
+          <t>needs_assessment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Needs Assessment'}</t>
+          <t>Needs Assessment</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'needs_analysis'}</t>
+          <t>needs_analysis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Needs Analysis'}</t>
+          <t>Needs Analysis</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'needs_analysis_and_assessment'}</t>
+          <t>needs_analysis_and_assessment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Needs Analysis and Assessment'}</t>
+          <t>Needs Analysis and Assessment</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'request_1'}</t>
+          <t>request_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Request 1'}</t>
+          <t>Request 1</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'request_2'}</t>
+          <t>request_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Request 2'}</t>
+          <t>Request 2</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'request_3'}</t>
+          <t>request_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Request 3'}</t>
+          <t>Request 3</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'phone_and_email'}</t>
+          <t>phone_and_email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Phone and Email'}</t>
+          <t>Phone and Email</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'form_completed_by'}</t>
+          <t>form_completed_by</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Form Completed By'}</t>
+          <t>Form Completed By</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'not_given'}</t>
+          <t>not_given</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'Not Given'}</t>
+          <t>Not Given</t>
         </is>
       </c>
     </row>
